--- a/out/Attention-MambaAMT_repeat_4_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.378954327415217</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.378954327415217</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.378954327415217</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6427816135952731</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.242781613595273</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.378954327415217</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6427816135952731</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6427816135952731</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.242781613595273</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.378954327415217</v>
+        <v>2.499999930000002</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.378954327415217</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.378954327415217</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.378954327415217</v>
+        <v>3.099999930000001</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002943019607702736</v>
+        <v>-6.732996095530688e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1267178795703224</v>
+        <v>0.02899021925981118</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.3999999825000004</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2537739356581026</v>
+        <v>0.058058020720931</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4895773565666943</v>
+        <v>0.1120053759499557</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.106536475653377</v>
+        <v>0.2531524751708785</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1505972483212504</v>
+        <v>0.03445297250026079</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.917532195259691</v>
+        <v>0.2099122740289848</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03055709535984692</v>
+        <v>0.006990600123608994</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8278139564481205</v>
+        <v>0.1893859546170388</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02646416041534731</v>
+        <v>0.006052574990285557</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.850150987053171</v>
+        <v>0.1944943215840454</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01293737758466283</v>
+        <v>0.002956074988161011</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8495281459893003</v>
+        <v>0.1943483495095894</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006172914716297172</v>
+        <v>0.001408182957491728</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8489205926820801</v>
+        <v>0.1942054850224892</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00256867126865702</v>
+        <v>0.0005839993948170295</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8478779277208203</v>
+        <v>0.1939630094592157</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001778332813450368</v>
+        <v>0.0004032142182238185</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8488643641839518</v>
+        <v>0.1941849051917361</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007397957993560148</v>
+        <v>0.0001650917742473944</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8485629118560614</v>
+        <v>0.1941120757385129</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003812031912199617</v>
+        <v>8.319865266615043e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8485847462246033</v>
+        <v>0.1941132279158924</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001466857209841172</v>
+        <v>2.964102970571534e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8484964600230672</v>
+        <v>0.1940890640579865</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.745918963236801e-05</v>
+        <v>1.389689762408434e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8485050967831237</v>
+        <v>0.1940872260151447</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.565636471755614e-05</v>
+        <v>4.599419447200756e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8484988491042599</v>
+        <v>0.1940819333063658</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.41817221615223e-05</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8484914769869991</v>
+        <v>0.1940763813702362</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8484838018832852</v>
+        <v>0.1940707311050829</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8484778833304143</v>
+        <v>0.194065489783782</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8484719219018297</v>
+        <v>0.1940602018449316</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8484662427251216</v>
+        <v>0.1940549300108806</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8484613614268722</v>
+        <v>0.1940549698663528</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8484564402253244</v>
+        <v>0.1940550097218251</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.84845643225423</v>
+        <v>0.1940550017507307</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.848456591676119</v>
+        <v>0.1940551611726198</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8484568467511419</v>
+        <v>0.1940554162476426</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8484565996472134</v>
+        <v>0.1940551691437142</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8484565597917412</v>
+        <v>0.194055129288242</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.1940551372593364</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8484565996472134</v>
+        <v>0.1940551691437142</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8484566953003472</v>
+        <v>0.194055264796848</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8484566315315913</v>
+        <v>0.1940552010280921</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.848456591676119</v>
+        <v>0.1940551611726198</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.1940551372593364</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8484563206589075</v>
+        <v>0.1940548901554083</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8484562409479628</v>
+        <v>0.1940548104444635</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8484562887745295</v>
+        <v>0.1940548582710303</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8484564083409465</v>
+        <v>0.1940549778374473</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8484563923987576</v>
+        <v>0.1940549618952584</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8484564083409465</v>
+        <v>0.1940549778374473</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8484563923987576</v>
+        <v>0.1940549618952584</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.1940550176929196</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.1940550176929196</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.1940550176929196</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8484565996472134</v>
+        <v>0.1940551691437142</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8484568148667641</v>
+        <v>0.1940553843632648</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.848456727184725</v>
+        <v>0.1940552966812258</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8484566793581583</v>
+        <v>0.194055248854659</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.848456727184725</v>
+        <v>0.1940552966812258</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8484565438495523</v>
+        <v>0.194055113346053</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8484565518206467</v>
+        <v>0.1940551213171475</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.778954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8484565597917412</v>
+        <v>0.194055129288242</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.1940551372593364</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.1940551372593364</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8484566076183079</v>
+        <v>0.1940551771148087</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8484566713870638</v>
+        <v>0.1940552408835646</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8484567829823861</v>
+        <v>0.1940553524788869</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.848456830808953</v>
+        <v>0.1940554003054537</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8484567909534806</v>
+        <v>0.1940553604499814</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8484567192136305</v>
+        <v>0.1940552887101313</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8484568387800474</v>
+        <v>0.1940554082765481</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8484566793581583</v>
+        <v>0.194055248854659</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.1940550176929196</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.848456400369852</v>
+        <v>0.1940549698663528</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.84845643225423</v>
+        <v>0.1940550017507307</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8484564163120409</v>
+        <v>0.1940549858085418</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.848456296745624</v>
+        <v>0.1940548662421247</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8484562568901517</v>
+        <v>0.1940548263866524</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.848456400369852</v>
+        <v>0.1940549698663528</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8484565358784578</v>
+        <v>0.1940551053749586</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8484565199362689</v>
+        <v>0.1940550894327697</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8484564561675133</v>
+        <v>0.194055025664014</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8484563525432853</v>
+        <v>0.1940549220397861</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8484562329768682</v>
+        <v>0.1940548024733691</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8484563525432853</v>
+        <v>0.1940549220397861</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.848456400369852</v>
+        <v>0.1940549698663528</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.1940550655194863</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.378954327415217</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8484563764565687</v>
+        <v>0.1940549459530695</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.9999999825000003</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8484563844276631</v>
+        <v>0.1940549539241639</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.378954327415217</v>
+        <v>0.004203680051353333</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002943019607702736</v>
+        <v>-0.0002295018438864499</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1267178795703224</v>
+        <v>0.09881683064104536</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2537739356581026</v>
+        <v>0.1978973772767533</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4895773565666943</v>
+        <v>0.381781676369493</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.106536475653377</v>
+        <v>0.8628965993102752</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1505972483212504</v>
+        <v>0.1174381838092836</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.917532195259691</v>
+        <v>0.7155079871739736</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03055709535984692</v>
+        <v>0.02382887451173678</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.778954327415217</v>
+        <v>0.004203680051353256</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8278139564481205</v>
+        <v>0.6455442453701047</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02646416041534731</v>
+        <v>0.02063722213932391</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.6948861808537511</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.850150987053171</v>
+        <v>0.6629630584098706</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01293737758466283</v>
+        <v>0.01008906953495419</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.778954327415217</v>
+        <v>0.6948861808537511</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8495281459893003</v>
+        <v>0.6624773551891336</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006172914716297172</v>
+        <v>0.004812517316082914</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.778954327415217</v>
+        <v>1.385568681656149</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8489205926820801</v>
+        <v>0.662002486127371</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00256867126865702</v>
+        <v>0.002001940281961617</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8478779277208203</v>
+        <v>0.6611883184472189</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001778332813450368</v>
+        <v>0.001385552025027072</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8488643641839518</v>
+        <v>0.6619564374663944</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007397957993560148</v>
+        <v>0.0005755026083215997</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.778954327415217</v>
+        <v>0.004203680051353256</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8485629118560614</v>
+        <v>0.6617202514968508</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003812031912199617</v>
+        <v>0.0002963453966093473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353256</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8485847462246033</v>
+        <v>0.6617361897325125</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001466857209841172</v>
+        <v>0.0001130944194513023</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.8484964600230672</v>
+        <v>0.6616662040543845</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>7.745918963236801e-05</v>
+        <v>5.970755853095545e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8485050967831237</v>
+        <v>0.66167186759247</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.565636471755614e-05</v>
+        <v>2.662161700254366e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8484988491042599</v>
+        <v>0.6616658954042217</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.41817221615223e-05</v>
+        <v>9.919117236739567e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8484914769869991</v>
+        <v>0.6616590433387123</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.301093358848441e-06</v>
+        <v>1.456405945771008e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8484838018832852</v>
+        <v>0.6616519467603015</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.8484778833304143</v>
+        <v>0.6616462217021649</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8484719219018297</v>
+        <v>0.6616404525592975</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8484662427251216</v>
+        <v>0.6616349088911949</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8484613614268722</v>
+        <v>0.6616299877374736</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.8484564402253244</v>
+        <v>0.6616300275929459</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.84845643225423</v>
+        <v>0.6616300196218514</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.848456591676119</v>
+        <v>0.6616301790437406</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8484568467511419</v>
+        <v>0.6616304341187633</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8484565996472134</v>
+        <v>0.661630187014835</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8484565597917412</v>
+        <v>0.6616301471593626</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.6616301551304571</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8484565996472134</v>
+        <v>0.661630187014835</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8484566953003472</v>
+        <v>0.6616302826679686</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8484566315315913</v>
+        <v>0.6616302188992128</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.848456591676119</v>
+        <v>0.6616301790437406</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.6616301551304571</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8484563206589075</v>
+        <v>0.661629908026529</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.378954327415217</v>
+        <v>0.004203680051353333</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8484562409479628</v>
+        <v>0.6616298283155843</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537513</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8484562887745295</v>
+        <v>0.661629876142151</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8484564083409465</v>
+        <v>0.6616299957085681</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513534</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8484563923987576</v>
+        <v>0.6616299797663792</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8484564083409465</v>
+        <v>0.6616299957085681</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8484563923987576</v>
+        <v>0.6616299797663792</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.6616300355640403</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.6616300355640403</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.6616300355640403</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.378954327415217</v>
+        <v>1.585568681656149</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8484565996472134</v>
+        <v>0.661630187014835</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8484568148667641</v>
+        <v>0.6616304022343855</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.848456727184725</v>
+        <v>0.6616303145523464</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8484566793581583</v>
+        <v>0.6616302667257797</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353256</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.848456727184725</v>
+        <v>0.6616303145523464</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353298</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8484565438495523</v>
+        <v>0.6616301312171737</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.778954327415217</v>
+        <v>0.6948861808537511</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8484565518206467</v>
+        <v>0.6616301391882682</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.778954327415217</v>
+        <v>0.6948861808537511</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8484565597917412</v>
+        <v>0.6616301471593626</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.6616301551304571</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8484565677628356</v>
+        <v>0.6616301551304571</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537512</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8484566076183079</v>
+        <v>0.6616301949859295</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513533</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8484566713870638</v>
+        <v>0.6616302587546853</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8484567829823861</v>
+        <v>0.6616303703500077</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.848456830808953</v>
+        <v>0.6616304181765744</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8484567909534806</v>
+        <v>0.6616303783211022</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8484567192136305</v>
+        <v>0.661630306581252</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.8484568387800474</v>
+        <v>0.6616304261476689</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8484566793581583</v>
+        <v>0.6616302667257797</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8484564481964189</v>
+        <v>0.6616300355640403</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353152</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.848456400369852</v>
+        <v>0.6616299877374736</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513532</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.84845643225423</v>
+        <v>0.6616300196218514</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513532</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8484564163120409</v>
+        <v>0.6616300036796625</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353152</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.848456296745624</v>
+        <v>0.6616298841132454</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537509</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8484562568901517</v>
+        <v>0.6616298442577732</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.378954327415217</v>
+        <v>0.8948861808537509</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.848456400369852</v>
+        <v>0.6616299877374736</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.2042036800513531</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8484565358784578</v>
+        <v>0.6616301232460793</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6427816135952731</v>
+        <v>-0.4864788207510444</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8484565199362689</v>
+        <v>0.6616301073038904</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.242781613595273</v>
+        <v>-0.6864788207510445</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8484564561675133</v>
+        <v>0.6616300435351348</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.242781613595273</v>
+        <v>0.004203680051353013</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.8484563525432853</v>
+        <v>0.6616299399109068</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.378954327415217</v>
+        <v>0.004203680051353048</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8484562329768682</v>
+        <v>0.6616298203444898</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537509</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.8484563525432853</v>
+        <v>0.6616299399109068</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513531</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.848456400369852</v>
+        <v>0.6616299877374736</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.8948861808537509</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8484564960229856</v>
+        <v>0.661630083390607</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>2.378954327415217</v>
+        <v>0.2042036800513531</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8484563764565687</v>
+        <v>0.6616299638241901</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6427816135952731</v>
+        <v>0.5495449304525518</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8484563844276631</v>
+        <v>0.6616299717952847</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_4_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_4_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01811587996780872</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.006695037707686424</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.01848501339554787</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.01113607361912727</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.01431543566286564</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.008595813065767288</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.006036240607500076</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.001406379044055939</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.01488381996750832</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.004203680051353298</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.001132646575570107</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.01198821142315865</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.000847838819026947</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.01406104303896427</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.2042036800513533</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.006453657522797585</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01812609098851681</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.585568681656149</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0159327145665884</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.01996165700256824</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.2042036800513533</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.004514800384640694</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.01260943710803986</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.01708120666444302</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.01651380769908428</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.01775114424526691</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.008475471287965775</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.004203680051353298</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001325841993093491</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.004203680051353333</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.01332746725529432</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.2042036800513534</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.01603845320641994</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.16</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.01407337561249733</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.005740107968449593</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.008174419403076172</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.004203680051353298</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.0004943683743476868</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.01346712373197079</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.01329303160309792</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.3</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.005998900160193443</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.001577576622366905</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.004203680051353298</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.000464489683508873</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.2042036800513533</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.007912429049611092</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.2042036800513533</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.007419930770993233</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.4864788207510444</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.009743174538016319</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.004203680051353298</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.03604345768690109</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.03764203190803528</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.585568681656149</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.06565360724925995</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.585568681656149</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.0420796200633049</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.585568681656149</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002295018438864499</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.09881683064104536</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0536189004778862</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.585568681656149</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1978973772767533</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.381781676369493</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0355432853102684</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8628965993102752</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1174381838092836</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.009614204987883568</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8948861808537512</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7155079871739736</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02382887451173678</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.0359027162194252</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.004203680051353256</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6455442453701047</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02063722213932391</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01938195154070854</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.6948861808537511</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6629630584098706</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01008906953495419</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.02094783820211887</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6948861808537511</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6624773551891336</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004812517316082914</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0009477753192186356</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.385568681656149</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.662002486127371</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002001940281961617</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.009322101250290871</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8948861808537512</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6611883184472189</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001385552025027072</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.00326160155236721</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8948861808537512</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6619564374663944</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005755026083215997</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02321634255349636</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.004203680051353256</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6617202514968508</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002963453966093473</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.003165746107697487</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.004203680051353256</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6617361897325125</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001130944194513023</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.02030217461287975</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6616662040543845</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>5.970755853095545e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.01579699851572514</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.66167186759247</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.662161700254366e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.01065809838473797</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6616658954042217</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>9.919117236739567e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.01017062366008759</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6616590433387123</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.456405945771008e-06</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.02129307948052883</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6616519467603015</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.01051951013505459</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6616462217021649</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.02873966656625271</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6616404525592975</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.01220338419079781</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6616349088911949</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.006310617551207542</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6616299877374736</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.01875809021294117</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2042036800513533</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6616300275929459</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.006148533895611763</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.6616300196218514</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.0206145066767931</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6616301790437406</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.03175751119852066</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01951884850859642</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.2042036800513534</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6616304341187633</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.03131910413503647</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.4864788207510444</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.661630187014835</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.006734983995556831</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6616301471593626</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.007840031757950783</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009373355656862259</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.004203680051353298</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6616301551304571</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.009216116741299629</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.03950309008359909</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.661630187014835</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.008725661784410477</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.2042036800513533</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6616302826679686</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.02878783456981182</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6616302188992128</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.001776127144694328</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6616301790437406</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.03049903735518456</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6616301551304571</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.0268056932836771</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.004203680051353298</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.661629908026529</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.00364876352250576</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.004203680051353333</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6616298283155843</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.001794340088963509</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.8948861808537513</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.661629876142151</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.005473868921399117</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6616299957085681</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.0002243239432573318</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.2042036800513534</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6616299797663792</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.006902823224663734</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6616299957085681</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.004049621522426605</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6616299797663792</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01218281686306</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.004203680051353298</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6616300355640403</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.0146769043058157</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8948861808537512</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6616300355640403</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.009732166305184364</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.585568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6616300355640403</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.001059083268046379</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.585568681656149</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.661630187014835</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.004815505817532539</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.8948861808537512</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6616304022343855</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01610142551362514</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.8948861808537512</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6616303145523464</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.003408804535865784</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.2042036800513533</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6616302667257797</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.03252039849758148</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.004203680051353256</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6616303145523464</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.002475949004292488</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.004203680051353298</v>
+        <v>-0.3</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6616301312171737</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.004049981012940407</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6948861808537511</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6616301391882682</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.00231221504509449</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6948861808537511</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6616301471593626</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0001237746328115463</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6616301551304571</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.01571105979382992</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6616301551304571</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.004818292334675789</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8948861808537512</v>
+        <v>0.3</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.6616301949859295</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.006555227562785149</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.2042036800513533</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6616302587546853</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.00652836449444294</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6616303703500077</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.01430961862206459</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.6616304181765744</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.01759894378483295</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6616303783211022</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.002064215019345284</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.661630306581252</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.02074029296636581</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6616304261476689</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.03022309392690659</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6616302667257797</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.02033070847392082</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6864788207510445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6616300355640403</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01733228005468845</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.004203680051353152</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6616299877374736</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.004157332703471184</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.2042036800513532</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.6616300196218514</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.008539814502000809</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.2042036800513532</v>
+        <v>0.16</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.007392691448330879</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.16</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.001525992527604103</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6616300036796625</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.01565020717680454</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.004203680051353152</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.6616298841132454</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01028168387711048</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.8948861808537509</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6616298442577732</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.003229381516575813</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8948861808537509</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6616299877374736</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003397200256586075</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.2042036800513531</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.6616301232460793</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.001994950696825981</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4864788207510444</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6616301073038904</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.001428486779332161</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003043748438358307</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6864788207510445</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6616300435351348</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02596965059638023</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.004203680051353013</v>
+        <v>-0.3</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6616299399109068</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.001801369711756706</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.004203680051353048</v>
+        <v>-0.3</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6616298203444898</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.007666582241654396</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.8948861808537509</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6616299399109068</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.0004205070436000824</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.2042036800513531</v>
+        <v>-0.16</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6616299877374736</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.008226918056607246</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8948861808537509</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.661630083390607</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.001240011304616928</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.2042036800513531</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6616299638241901</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.01106773316860199</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.5495449304525518</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6616299717952847</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>
